--- a/database/event/4866/event_4866_evp_summary.xlsx
+++ b/database/event/4866/event_4866_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.381</v>
+        <v>10.2829</v>
       </c>
       <c r="C2" t="n">
-        <v>4.9471</v>
+        <v>5.4227</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3684</v>
+        <v>3.6528</v>
       </c>
       <c r="E2" t="n">
-        <v>9.381</v>
+        <v>10.2829</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8598</v>
+        <v>3.7618</v>
       </c>
       <c r="G2" t="n">
         <v>6.5212</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8598</v>
+        <v>3.7618</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8598</v>
+        <v>3.7618</v>
       </c>
       <c r="J2" t="n">
         <v>6.8601</v>
@@ -529,7 +529,7 @@
         <v>167</v>
       </c>
       <c r="M2" t="n">
-        <v>9.719899999999999</v>
+        <v>10.6219</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.9601</v>
+        <v>8.201599999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1978</v>
+        <v>4.3252</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7943</v>
+        <v>2.8236</v>
       </c>
       <c r="E3" t="n">
-        <v>7.9601</v>
+        <v>8.201599999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5186</v>
+        <v>2.7601</v>
       </c>
       <c r="G3" t="n">
         <v>5.4415</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5186</v>
+        <v>2.7601</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5186</v>
+        <v>2.7601</v>
       </c>
       <c r="J3" t="n">
         <v>5.4415</v>
@@ -575,7 +575,7 @@
         <v>210</v>
       </c>
       <c r="M3" t="n">
-        <v>7.9601</v>
+        <v>8.201599999999999</v>
       </c>
       <c r="N3" t="n">
         <v>314</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2117</v>
+        <v>6.3956</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2758</v>
+        <v>3.3728</v>
       </c>
       <c r="D4" t="n">
-        <v>2.088</v>
+        <v>2.1041</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2117</v>
+        <v>6.3956</v>
       </c>
       <c r="F4" t="n">
-        <v>2.615</v>
+        <v>2.7989</v>
       </c>
       <c r="G4" t="n">
         <v>3.5967</v>
       </c>
       <c r="H4" t="n">
-        <v>2.615</v>
+        <v>2.7989</v>
       </c>
       <c r="I4" t="n">
-        <v>2.615</v>
+        <v>2.7989</v>
       </c>
       <c r="J4" t="n">
         <v>3.5967</v>
@@ -621,7 +621,7 @@
         <v>167</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2117</v>
+        <v>6.3956</v>
       </c>
       <c r="N4" t="n">
         <v>264</v>
@@ -630,231 +630,231 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.5262</v>
+        <v>6.0317</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9143</v>
+        <v>3.1809</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8111</v>
+        <v>1.9591</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5262</v>
+        <v>6.0317</v>
       </c>
       <c r="F5" t="n">
-        <v>4.744</v>
+        <v>3.4804</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7822</v>
+        <v>2.5513</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1356</v>
+        <v>3.4804</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1835</v>
+        <v>3.4804</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7822</v>
+        <v>2.5513</v>
       </c>
       <c r="K5" t="n">
-        <v>301</v>
+        <v>97</v>
       </c>
       <c r="L5" t="n">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9657</v>
+        <v>6.0317</v>
       </c>
       <c r="N5" t="n">
-        <v>357</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.2942</v>
+        <v>5.5018</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7919</v>
+        <v>2.9014</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7174</v>
+        <v>1.748</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2942</v>
+        <v>5.5018</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7429</v>
+        <v>4.7196</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5513</v>
+        <v>0.7822</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7429</v>
+        <v>5.0973</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7429</v>
+        <v>5.1835</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5513</v>
+        <v>0.7822</v>
       </c>
       <c r="K6" t="n">
-        <v>97</v>
+        <v>301</v>
       </c>
       <c r="L6" t="n">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2942</v>
+        <v>5.9657</v>
       </c>
       <c r="N6" t="n">
-        <v>264</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8427</v>
+        <v>4.424</v>
       </c>
       <c r="C7" t="n">
-        <v>2.0265</v>
+        <v>2.333</v>
       </c>
       <c r="D7" t="n">
-        <v>1.131</v>
+        <v>1.3186</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8427</v>
+        <v>4.424</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4256</v>
+        <v>4.3229</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4171</v>
+        <v>0.1011</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4256</v>
+        <v>4.4752</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4256</v>
+        <v>4.4752</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4171</v>
+        <v>0.1011</v>
       </c>
       <c r="K7" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="L7" t="n">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8427</v>
+        <v>4.5763</v>
       </c>
       <c r="N7" t="n">
-        <v>234</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.677</v>
+        <v>3.8555</v>
       </c>
       <c r="C8" t="n">
-        <v>1.9391</v>
+        <v>2.0332</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0641</v>
+        <v>1.0921</v>
       </c>
       <c r="E8" t="n">
-        <v>3.677</v>
+        <v>3.8555</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5759</v>
+        <v>3.4384</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1011</v>
+        <v>0.4171</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5759</v>
+        <v>3.4384</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5759</v>
+        <v>3.4384</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1011</v>
+        <v>0.4171</v>
       </c>
       <c r="K8" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L8" t="n">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="M8" t="n">
-        <v>3.677</v>
+        <v>3.8555</v>
       </c>
       <c r="N8" t="n">
-        <v>325</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6302</v>
+        <v>3.8311</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9144</v>
+        <v>2.0204</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0452</v>
+        <v>1.0824</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6302</v>
+        <v>3.8311</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9525</v>
+        <v>2.6941</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6777</v>
+        <v>1.137</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9525</v>
+        <v>2.6941</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9663</v>
+        <v>2.6941</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6777</v>
+        <v>1.137</v>
       </c>
       <c r="K9" t="n">
-        <v>250</v>
+        <v>104</v>
       </c>
       <c r="L9" t="n">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="M9" t="n">
-        <v>3.644</v>
+        <v>3.8311</v>
       </c>
       <c r="N9" t="n">
-        <v>333</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6207</v>
+        <v>3.7339</v>
       </c>
       <c r="C10" t="n">
-        <v>1.9094</v>
+        <v>1.9691</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0413</v>
+        <v>1.0437</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6207</v>
+        <v>3.7339</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9508</v>
+        <v>2.064</v>
       </c>
       <c r="G10" t="n">
         <v>1.6699</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9508</v>
+        <v>2.064</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9508</v>
+        <v>2.064</v>
       </c>
       <c r="J10" t="n">
         <v>1.6699</v>
@@ -897,7 +897,7 @@
         <v>171</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6207</v>
+        <v>3.7339</v>
       </c>
       <c r="N10" t="n">
         <v>325</v>
@@ -906,550 +906,550 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1108</v>
+        <v>3.6192</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6405</v>
+        <v>1.9086</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8353</v>
+        <v>0.998</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1108</v>
+        <v>3.6192</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3805</v>
+        <v>2.9415</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7303</v>
+        <v>0.6777</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3805</v>
+        <v>2.9415</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3805</v>
+        <v>2.9663</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7303</v>
+        <v>0.6777</v>
       </c>
       <c r="K11" t="n">
-        <v>104</v>
+        <v>250</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1108</v>
+        <v>3.644</v>
       </c>
       <c r="N11" t="n">
-        <v>314</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>nicoodoz</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0442</v>
+        <v>3.3251</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6054</v>
+        <v>1.7535</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8084</v>
+        <v>0.8808</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0442</v>
+        <v>3.3251</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9072</v>
+        <v>3.3251</v>
       </c>
       <c r="G12" t="n">
-        <v>1.137</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9072</v>
+        <v>3.3251</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9072</v>
+        <v>3.3251</v>
       </c>
       <c r="J12" t="n">
-        <v>1.137</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>104</v>
+        <v>234</v>
       </c>
       <c r="L12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0442</v>
+        <v>3.3251</v>
       </c>
       <c r="N12" t="n">
-        <v>314</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nicoodoz</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0091</v>
+        <v>3.2367</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5869</v>
+        <v>1.7069</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7942</v>
+        <v>0.8456</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0091</v>
+        <v>3.2367</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0091</v>
+        <v>3.4269</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.1902</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0091</v>
+        <v>3.4269</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0091</v>
+        <v>3.4269</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.1902</v>
       </c>
       <c r="K13" t="n">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0091</v>
+        <v>3.2367</v>
       </c>
       <c r="N13" t="n">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9403</v>
+        <v>3.1961</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5506</v>
+        <v>1.6855</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7665</v>
+        <v>0.8294</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9403</v>
+        <v>3.1961</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9403</v>
+        <v>3.7254</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.5293</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9403</v>
+        <v>3.7254</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9403</v>
+        <v>3.7254</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.5293</v>
       </c>
       <c r="K14" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9403</v>
+        <v>3.1961</v>
       </c>
       <c r="N14" t="n">
-        <v>218</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.911</v>
+        <v>3.1108</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5351</v>
+        <v>1.6405</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7546</v>
+        <v>0.7954</v>
       </c>
       <c r="E15" t="n">
-        <v>2.911</v>
+        <v>3.1108</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3053</v>
+        <v>1.3805</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3943</v>
+        <v>1.7303</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3053</v>
+        <v>1.3805</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3361</v>
+        <v>1.3805</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3943</v>
+        <v>1.7303</v>
       </c>
       <c r="K15" t="n">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="L15" t="n">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9418</v>
+        <v>3.1108</v>
       </c>
       <c r="N15" t="n">
-        <v>357</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7487</v>
+        <v>2.9949</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4495</v>
+        <v>1.5794</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6891</v>
+        <v>0.7493</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7487</v>
+        <v>2.9949</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7487</v>
+        <v>1.9229</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.072</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7487</v>
+        <v>1.9229</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7487</v>
+        <v>1.9229</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.072</v>
       </c>
       <c r="K16" t="n">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M16" t="n">
-        <v>2.7487</v>
+        <v>2.9949</v>
       </c>
       <c r="N16" t="n">
-        <v>185</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6756</v>
+        <v>2.9403</v>
       </c>
       <c r="C17" t="n">
-        <v>1.411</v>
+        <v>1.5506</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6595</v>
+        <v>0.7275</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6756</v>
+        <v>2.9403</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4083</v>
+        <v>2.9403</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2673</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4083</v>
+        <v>2.9403</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4083</v>
+        <v>2.9403</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2673</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="L17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6756</v>
+        <v>2.9403</v>
       </c>
       <c r="N17" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.6115</v>
+        <v>2.8863</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3772</v>
+        <v>1.5221</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6115</v>
+        <v>2.8863</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8017</v>
+        <v>3.2806</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1902</v>
+        <v>-0.3943</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8017</v>
+        <v>3.2806</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8017</v>
+        <v>3.3361</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1902</v>
+        <v>-0.3943</v>
       </c>
       <c r="K18" t="n">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="L18" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M18" t="n">
-        <v>2.6115</v>
+        <v>2.9418</v>
       </c>
       <c r="N18" t="n">
-        <v>212</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4918</v>
+        <v>2.8578</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3141</v>
+        <v>1.5071</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5853</v>
+        <v>0.6946</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4918</v>
+        <v>2.8578</v>
       </c>
       <c r="F19" t="n">
-        <v>2.758</v>
+        <v>2.5905</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2662</v>
+        <v>0.2673</v>
       </c>
       <c r="H19" t="n">
-        <v>2.758</v>
+        <v>2.5905</v>
       </c>
       <c r="I19" t="n">
-        <v>2.758</v>
+        <v>2.5905</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2662</v>
+        <v>0.2673</v>
       </c>
       <c r="K19" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="L19" t="n">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4918</v>
+        <v>2.8578</v>
       </c>
       <c r="N19" t="n">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2765</v>
+        <v>2.7487</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2005</v>
+        <v>1.4495</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4983</v>
+        <v>0.6512</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2765</v>
+        <v>2.7487</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2045</v>
+        <v>2.7487</v>
       </c>
       <c r="G20" t="n">
-        <v>1.072</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2045</v>
+        <v>2.7487</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2045</v>
+        <v>2.7487</v>
       </c>
       <c r="J20" t="n">
-        <v>1.072</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="L20" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2765</v>
+        <v>2.7487</v>
       </c>
       <c r="N20" t="n">
-        <v>234</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2448</v>
+        <v>2.7429</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1838</v>
+        <v>1.4465</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4855</v>
+        <v>0.6489</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2448</v>
+        <v>2.7429</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7741</v>
+        <v>2.7429</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5293</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.7741</v>
+        <v>2.7429</v>
       </c>
       <c r="I21" t="n">
-        <v>2.7741</v>
+        <v>2.7429</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5293</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.2448</v>
+        <v>2.7429</v>
       </c>
       <c r="N21" t="n">
-        <v>291</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0925</v>
+        <v>2.6792</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1035</v>
+        <v>1.4129</v>
       </c>
       <c r="D22" t="n">
-        <v>0.424</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0925</v>
+        <v>2.6792</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0925</v>
+        <v>2.9454</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.2662</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0925</v>
+        <v>2.9454</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0925</v>
+        <v>2.9454</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.2662</v>
       </c>
       <c r="K22" t="n">
-        <v>234</v>
+        <v>129</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0925</v>
+        <v>2.6792</v>
       </c>
       <c r="N22" t="n">
         <v>234</v>
@@ -1458,737 +1458,737 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bymas</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8817</v>
+        <v>2.657</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9923</v>
+        <v>1.4012</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3388</v>
+        <v>0.6146</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8817</v>
+        <v>2.657</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8817</v>
+        <v>2.657</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8817</v>
+        <v>2.657</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8817</v>
+        <v>2.657</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>185</v>
+        <v>234</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8817</v>
+        <v>2.657</v>
       </c>
       <c r="N23" t="n">
-        <v>185</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8554</v>
+        <v>2.5458</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9785</v>
+        <v>1.3425</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3282</v>
+        <v>0.5703</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8554</v>
+        <v>2.5458</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3052</v>
+        <v>2.772</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4498</v>
+        <v>-0.2262</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3052</v>
+        <v>2.772</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3052</v>
+        <v>2.772</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4498</v>
+        <v>-0.2262</v>
       </c>
       <c r="K24" t="n">
-        <v>104</v>
+        <v>237</v>
       </c>
       <c r="L24" t="n">
-        <v>210</v>
+        <v>54</v>
       </c>
       <c r="M24" t="n">
-        <v>1.8554</v>
+        <v>2.5458</v>
       </c>
       <c r="N24" t="n">
-        <v>314</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.8141</v>
+        <v>1.9785</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9567</v>
+        <v>1.0434</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3115</v>
+        <v>0.3443</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8141</v>
+        <v>1.9785</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0403</v>
+        <v>3.2235</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2262</v>
+        <v>-1.245</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0403</v>
+        <v>3.2235</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0403</v>
+        <v>3.2235</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2262</v>
+        <v>-1.245</v>
       </c>
       <c r="K25" t="n">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="L25" t="n">
-        <v>54</v>
+        <v>171</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8141</v>
+        <v>1.9785</v>
       </c>
       <c r="N25" t="n">
-        <v>291</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>El1an</t>
+          <t>Bymas</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7811</v>
+        <v>1.8817</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9393</v>
+        <v>0.9923</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2982</v>
+        <v>0.3058</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7811</v>
+        <v>1.8817</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7811</v>
+        <v>1.8817</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7811</v>
+        <v>1.8817</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7811</v>
+        <v>1.8817</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>258</v>
+        <v>185</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7811</v>
+        <v>1.8817</v>
       </c>
       <c r="N26" t="n">
-        <v>258</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.7641</v>
+        <v>1.8554</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9303</v>
+        <v>0.9785</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2913</v>
+        <v>0.2953</v>
       </c>
       <c r="E27" t="n">
-        <v>1.7641</v>
+        <v>1.8554</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9523</v>
+        <v>2.3052</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8118</v>
+        <v>-0.4498</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9523</v>
+        <v>2.3052</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9523</v>
+        <v>2.3052</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8118</v>
+        <v>-0.4498</v>
       </c>
       <c r="K27" t="n">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="L27" t="n">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="M27" t="n">
-        <v>1.7641</v>
+        <v>1.8554</v>
       </c>
       <c r="N27" t="n">
-        <v>325</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>El1an</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5862</v>
+        <v>1.8353</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8365</v>
+        <v>0.9679</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2194</v>
+        <v>0.2873</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5862</v>
+        <v>1.8353</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4223</v>
+        <v>1.8353</v>
       </c>
       <c r="G28" t="n">
-        <v>1.1639</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4223</v>
+        <v>1.8353</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4223</v>
+        <v>1.8353</v>
       </c>
       <c r="J28" t="n">
-        <v>1.1639</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="L28" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5862</v>
+        <v>1.8353</v>
       </c>
       <c r="N28" t="n">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5704</v>
+        <v>1.7926</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8282</v>
+        <v>0.9453</v>
       </c>
       <c r="D29" t="n">
-        <v>0.213</v>
+        <v>0.2703</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5704</v>
+        <v>1.7926</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5704</v>
+        <v>1.7926</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5704</v>
+        <v>1.7926</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5704</v>
+        <v>1.7926</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5704</v>
+        <v>1.7926</v>
       </c>
       <c r="N29" t="n">
-        <v>185</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.5266</v>
+        <v>1.7764</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8051</v>
+        <v>0.9368</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1954</v>
+        <v>0.2638</v>
       </c>
       <c r="E30" t="n">
-        <v>1.5266</v>
+        <v>1.7764</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5266</v>
+        <v>0.9646</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.8118</v>
       </c>
       <c r="H30" t="n">
-        <v>1.5266</v>
+        <v>0.9646</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5266</v>
+        <v>0.9646</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.8118</v>
       </c>
       <c r="K30" t="n">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5266</v>
+        <v>1.7764</v>
       </c>
       <c r="N30" t="n">
-        <v>218</v>
+        <v>325</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4501</v>
+        <v>1.7107</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7647</v>
+        <v>0.9021</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1644</v>
+        <v>0.2376</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4501</v>
+        <v>1.7107</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6508</v>
+        <v>0.5468</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2007</v>
+        <v>1.1639</v>
       </c>
       <c r="H31" t="n">
-        <v>1.6508</v>
+        <v>0.5468</v>
       </c>
       <c r="I31" t="n">
-        <v>1.6508</v>
+        <v>0.5468</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2007</v>
+        <v>1.1639</v>
       </c>
       <c r="K31" t="n">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="L31" t="n">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="M31" t="n">
-        <v>1.4501</v>
+        <v>1.7107</v>
       </c>
       <c r="N31" t="n">
-        <v>234</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3646</v>
+        <v>1.6755</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7196</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1299</v>
+        <v>0.2236</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3646</v>
+        <v>1.6755</v>
       </c>
       <c r="F32" t="n">
-        <v>2.6096</v>
+        <v>1.8762</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.245</v>
+        <v>-0.2007</v>
       </c>
       <c r="H32" t="n">
-        <v>2.6096</v>
+        <v>1.8762</v>
       </c>
       <c r="I32" t="n">
-        <v>2.6096</v>
+        <v>1.8762</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.245</v>
+        <v>-0.2007</v>
       </c>
       <c r="K32" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="L32" t="n">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3646</v>
+        <v>1.6755</v>
       </c>
       <c r="N32" t="n">
-        <v>325</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.3344</v>
+        <v>1.5704</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7037</v>
+        <v>0.8282</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1177</v>
+        <v>0.1817</v>
       </c>
       <c r="E33" t="n">
-        <v>1.3344</v>
+        <v>1.5704</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3344</v>
+        <v>1.5704</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3344</v>
+        <v>1.5704</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3344</v>
+        <v>1.5704</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3344</v>
+        <v>1.5704</v>
       </c>
       <c r="N33" t="n">
-        <v>234</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2852</v>
+        <v>1.5553</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6778</v>
+        <v>0.8202</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0978</v>
+        <v>0.1757</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2852</v>
+        <v>1.5553</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3196</v>
+        <v>1.5553</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0344</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.3196</v>
+        <v>1.5553</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3196</v>
+        <v>1.5553</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.0344</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>154</v>
+        <v>218</v>
       </c>
       <c r="L34" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2852</v>
+        <v>1.5553</v>
       </c>
       <c r="N34" t="n">
-        <v>325</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2544</v>
+        <v>1.4477</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6615</v>
+        <v>0.7635</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0854</v>
+        <v>0.1329</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2544</v>
+        <v>1.4477</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3515</v>
+        <v>1.4821</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6059</v>
+        <v>-0.0344</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3515</v>
+        <v>1.4821</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3515</v>
+        <v>1.4821</v>
       </c>
       <c r="J35" t="n">
-        <v>1.6059</v>
+        <v>-0.0344</v>
       </c>
       <c r="K35" t="n">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="L35" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2544</v>
+        <v>1.4477</v>
       </c>
       <c r="N35" t="n">
-        <v>264</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0714</v>
+        <v>1.2544</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6615</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0115</v>
+        <v>0.0558</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0714</v>
+        <v>1.2544</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0331</v>
+        <v>-0.3515</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.9617</v>
+        <v>1.6059</v>
       </c>
       <c r="H36" t="n">
-        <v>2.0331</v>
+        <v>-0.3515</v>
       </c>
       <c r="I36" t="n">
-        <v>2.0426</v>
+        <v>-0.3515</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9617</v>
+        <v>1.6059</v>
       </c>
       <c r="K36" t="n">
-        <v>250</v>
+        <v>97</v>
       </c>
       <c r="L36" t="n">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0809</v>
+        <v>1.2544</v>
       </c>
       <c r="N36" t="n">
-        <v>333</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zyphon</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9384</v>
+        <v>1.0712</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4949</v>
+        <v>0.5649</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0423</v>
+        <v>-0.0171</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9384</v>
+        <v>1.0712</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9384</v>
+        <v>2.0329</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.9617</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9384</v>
+        <v>2.0329</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9384</v>
+        <v>2.05</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.9617</v>
       </c>
       <c r="K37" t="n">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9384</v>
+        <v>1.0883</v>
       </c>
       <c r="N37" t="n">
-        <v>234</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Zyphon</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8619</v>
+        <v>1.0633</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4545</v>
+        <v>0.5607</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0732</v>
+        <v>-0.0203</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8619</v>
+        <v>1.0633</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8619</v>
+        <v>1.0633</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8619</v>
+        <v>1.0633</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8619</v>
+        <v>1.0633</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8619</v>
+        <v>1.0633</v>
       </c>
       <c r="N38" t="n">
-        <v>218</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39">
@@ -2204,7 +2204,7 @@
         <v>0.4543</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0733</v>
+        <v>-0.1007</v>
       </c>
       <c r="E39" t="n">
         <v>0.8615</v>
@@ -2250,7 +2250,7 @@
         <v>0.4072</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1094</v>
+        <v>-0.1363</v>
       </c>
       <c r="E40" t="n">
         <v>0.7722</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7018</v>
+        <v>0.7002</v>
       </c>
       <c r="C41" t="n">
-        <v>0.3701</v>
+        <v>0.3693</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1379</v>
+        <v>-0.165</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7018</v>
+        <v>0.7002</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4318</v>
+        <v>0.4302</v>
       </c>
       <c r="G41" t="n">
         <v>0.27</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4318</v>
+        <v>0.4302</v>
       </c>
       <c r="I41" t="n">
         <v>0.4338</v>
@@ -2332,216 +2332,216 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.527</v>
+        <v>0.5504</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2779</v>
+        <v>0.2903</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2085</v>
+        <v>-0.2246</v>
       </c>
       <c r="E42" t="n">
-        <v>0.527</v>
+        <v>0.5504</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5554</v>
+        <v>0.5504</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0284</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5554</v>
+        <v>0.5504</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5504</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.0284</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="L42" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5296000000000001</v>
+        <v>0.5504</v>
       </c>
       <c r="N42" t="n">
-        <v>333</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3453</v>
+        <v>0.5249</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1821</v>
+        <v>0.2768</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2819</v>
+        <v>-0.2348</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3453</v>
+        <v>0.5249</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3453</v>
+        <v>0.5533</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.0284</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3453</v>
+        <v>0.5533</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3453</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.0284</v>
       </c>
       <c r="K43" t="n">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3453</v>
+        <v>0.5296000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>218</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Krad</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.316</v>
+        <v>0.4141</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1666</v>
+        <v>0.2184</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2937</v>
+        <v>-0.2789</v>
       </c>
       <c r="E44" t="n">
-        <v>0.316</v>
+        <v>0.4141</v>
       </c>
       <c r="F44" t="n">
-        <v>0.316</v>
+        <v>0.4141</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.316</v>
+        <v>0.4141</v>
       </c>
       <c r="I44" t="n">
-        <v>0.316</v>
+        <v>0.4141</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.316</v>
+        <v>0.4141</v>
       </c>
       <c r="N44" t="n">
-        <v>151</v>
+        <v>258</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2293</v>
+        <v>0.3453</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1209</v>
+        <v>0.1821</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3287</v>
+        <v>-0.3063</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2293</v>
+        <v>0.3453</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0833</v>
+        <v>0.3453</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.854</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.0833</v>
+        <v>0.3453</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0934</v>
+        <v>0.3453</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.854</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>301</v>
+        <v>218</v>
       </c>
       <c r="L45" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2393999999999999</v>
+        <v>0.3453</v>
       </c>
       <c r="N45" t="n">
-        <v>357</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1744</v>
+        <v>0.3195</v>
       </c>
       <c r="C46" t="n">
-        <v>0.092</v>
+        <v>0.1685</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3509</v>
+        <v>-0.3166</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1744</v>
+        <v>0.3195</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1744</v>
+        <v>0.3195</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1744</v>
+        <v>0.3195</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1744</v>
+        <v>0.3195</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1744</v>
+        <v>0.3195</v>
       </c>
       <c r="N46" t="n">
         <v>139</v>
@@ -2562,584 +2562,584 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1085</v>
+        <v>0.2212</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0572</v>
+        <v>0.1167</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3775</v>
+        <v>-0.3558</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1085</v>
+        <v>0.2212</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7161</v>
+        <v>1.0752</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.6076</v>
+        <v>-0.854</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7161</v>
+        <v>1.0752</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7161</v>
+        <v>1.0934</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6076</v>
+        <v>-0.854</v>
       </c>
       <c r="K47" t="n">
-        <v>150</v>
+        <v>301</v>
       </c>
       <c r="L47" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1084999999999999</v>
+        <v>0.2393999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>212</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0125</v>
+        <v>0.1744</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0066</v>
+        <v>0.092</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4163</v>
+        <v>-0.3744</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0125</v>
+        <v>0.1744</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0125</v>
+        <v>0.1744</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0125</v>
+        <v>0.1744</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0125</v>
+        <v>0.1744</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0125</v>
+        <v>0.1744</v>
       </c>
       <c r="N48" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.012</v>
+        <v>0.111</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0063</v>
+        <v>0.0585</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4165</v>
+        <v>-0.3997</v>
       </c>
       <c r="E49" t="n">
-        <v>0.012</v>
+        <v>0.111</v>
       </c>
       <c r="F49" t="n">
-        <v>0.012</v>
+        <v>0.7186</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.6076</v>
       </c>
       <c r="H49" t="n">
-        <v>0.012</v>
+        <v>0.7186</v>
       </c>
       <c r="I49" t="n">
-        <v>0.012</v>
+        <v>0.7186</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.6076</v>
       </c>
       <c r="K49" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M49" t="n">
-        <v>0.012</v>
+        <v>0.111</v>
       </c>
       <c r="N49" t="n">
-        <v>139</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0244</v>
+        <v>0.0997</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0129</v>
+        <v>0.0526</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4312</v>
+        <v>-0.4042</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0244</v>
+        <v>0.0997</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0244</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-0.7113</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0244</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0244</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-0.7113</v>
       </c>
       <c r="K50" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0244</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="N50" t="n">
-        <v>95</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Lack1</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0917</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0484</v>
+        <v>0.0454</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4584</v>
+        <v>-0.4096</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0917</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6196</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.7113</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6196</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6196</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.7113</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="L51" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.0917</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>212</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Krad</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.146</v>
+        <v>0.0125</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.077</v>
+        <v>0.0066</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4803</v>
+        <v>-0.4389</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.146</v>
+        <v>0.0125</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.146</v>
+        <v>0.0125</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.146</v>
+        <v>0.0125</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.146</v>
+        <v>0.0125</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>258</v>
+        <v>118</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.146</v>
+        <v>0.0125</v>
       </c>
       <c r="N52" t="n">
-        <v>258</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2491</v>
+        <v>0.012</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1314</v>
+        <v>0.0063</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.522</v>
+        <v>-0.4391</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2491</v>
+        <v>0.012</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2491</v>
+        <v>0.012</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2491</v>
+        <v>0.012</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2491</v>
+        <v>0.012</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2491</v>
+        <v>0.012</v>
       </c>
       <c r="N53" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2898</v>
+        <v>-0.0244</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1528</v>
+        <v>-0.0129</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5384</v>
+        <v>-0.4536</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2898</v>
+        <v>-0.0244</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2898</v>
+        <v>-0.0244</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2898</v>
+        <v>-0.0244</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2898</v>
+        <v>-0.0244</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2898</v>
+        <v>-0.0244</v>
       </c>
       <c r="N54" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lack1</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3122</v>
+        <v>-0.2228</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1646</v>
+        <v>-0.1175</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5475</v>
+        <v>-0.5327</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3122</v>
+        <v>-0.2228</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3122</v>
+        <v>-0.2228</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3122</v>
+        <v>-0.2228</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3122</v>
+        <v>-0.2228</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3122</v>
+        <v>-0.2228</v>
       </c>
       <c r="N55" t="n">
-        <v>258</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4709</v>
+        <v>-0.2491</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2483</v>
+        <v>-0.1314</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6116</v>
+        <v>-0.5432</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4709</v>
+        <v>-0.2491</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4709</v>
+        <v>-0.2491</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4709</v>
+        <v>-0.2491</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4709</v>
+        <v>-0.2491</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4709</v>
+        <v>-0.2491</v>
       </c>
       <c r="N56" t="n">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5815</v>
+        <v>-0.2898</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3067</v>
+        <v>-0.1528</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6563</v>
+        <v>-0.5594</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5815</v>
+        <v>-0.2898</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.3152</v>
+        <v>-0.2898</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7337</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.3152</v>
+        <v>-0.2898</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.3152</v>
+        <v>-0.2898</v>
       </c>
       <c r="J57" t="n">
-        <v>0.7337</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>237</v>
+        <v>118</v>
       </c>
       <c r="L57" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.5814999999999999</v>
+        <v>-0.2898</v>
       </c>
       <c r="N57" t="n">
-        <v>291</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5901</v>
+        <v>-0.5815</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3112</v>
+        <v>-0.3067</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6597</v>
+        <v>-0.6756</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5901</v>
+        <v>-0.5815</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5901</v>
+        <v>-1.3152</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.7337</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5901</v>
+        <v>-1.3152</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5901</v>
+        <v>-1.3152</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.7337</v>
       </c>
       <c r="K58" t="n">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5901</v>
+        <v>-0.5814999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>151</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6001</v>
+        <v>-0.5901</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3165</v>
+        <v>-0.3112</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6637999999999999</v>
+        <v>-0.679</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6001</v>
+        <v>-0.5901</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6001</v>
+        <v>-0.5901</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6001</v>
+        <v>-0.5901</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6001</v>
+        <v>-0.5901</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6001</v>
+        <v>-0.5901</v>
       </c>
       <c r="N59" t="n">
         <v>151</v>
@@ -3160,185 +3160,185 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6001</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3549</v>
+        <v>-0.3165</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6932</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6001</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6001</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6001</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6001</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>234</v>
+        <v>151</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6001</v>
       </c>
       <c r="N60" t="n">
-        <v>234</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7683</v>
+        <v>-0.7664</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4052</v>
+        <v>-0.4042</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7317</v>
+        <v>-0.7492</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7683</v>
+        <v>-0.7664</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7683</v>
+        <v>-0.7664</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7683</v>
+        <v>-0.7664</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7683</v>
+        <v>-0.7664</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7683</v>
+        <v>-0.7664</v>
       </c>
       <c r="N61" t="n">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.788</v>
+        <v>-0.7683</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4156</v>
+        <v>-0.4052</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7397</v>
+        <v>-0.75</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.788</v>
+        <v>-0.7683</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.8716</v>
+        <v>-0.7683</v>
       </c>
       <c r="G62" t="n">
-        <v>0.08359999999999999</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.8716</v>
+        <v>-0.7683</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.8757</v>
+        <v>-0.7683</v>
       </c>
       <c r="J62" t="n">
-        <v>0.08359999999999999</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="L62" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7921</v>
+        <v>-0.7683</v>
       </c>
       <c r="N62" t="n">
-        <v>333</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7905</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4169</v>
+        <v>-0.4139</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7407</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7905</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.7905</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.7905</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.7905</v>
+        <v>-0.8757</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7905</v>
+        <v>-0.7921</v>
       </c>
       <c r="N63" t="n">
-        <v>139</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64">
@@ -3354,7 +3354,7 @@
         <v>-0.4318</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7521</v>
+        <v>-0.7701</v>
       </c>
       <c r="E64" t="n">
         <v>-0.8188</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8409</v>
+        <v>-0.8421</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4435</v>
+        <v>-0.4441</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7611</v>
+        <v>-0.7794</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8409</v>
+        <v>-0.8421</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1591</v>
+        <v>0.1579</v>
       </c>
       <c r="G65" t="n">
         <v>-1</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1591</v>
+        <v>0.1579</v>
       </c>
       <c r="I65" t="n">
         <v>0.1606</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4699</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7813</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>-0.891</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4919</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7982</v>
+        <v>-0.8155</v>
       </c>
       <c r="E67" t="n">
         <v>-0.9327</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5018</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8057</v>
+        <v>-0.823</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9515</v>
@@ -3584,7 +3584,7 @@
         <v>-0.6464</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9166</v>
+        <v>-0.9323</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2258</v>
@@ -3630,7 +3630,7 @@
         <v>-0.6556</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9236</v>
+        <v>-0.9392</v>
       </c>
       <c r="E70" t="n">
         <v>-1.2432</v>
@@ -3676,7 +3676,7 @@
         <v>-0.6765</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9396</v>
+        <v>-0.955</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2829</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.319</v>
+        <v>-1.3081</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6956</v>
+        <v>-0.6898</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9542</v>
+        <v>-0.9651</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.319</v>
+        <v>-1.3081</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.4682</v>
+        <v>-1.4573</v>
       </c>
       <c r="G72" t="n">
         <v>0.1492</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.4682</v>
+        <v>-1.4573</v>
       </c>
       <c r="I72" t="n">
         <v>-1.4819</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6962</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9547</v>
+        <v>-0.9698</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3201</v>
@@ -3804,139 +3804,139 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.4971</v>
+        <v>-1.4084</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7895</v>
+        <v>-0.7427</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0262</v>
+        <v>-1.005</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.4971</v>
+        <v>-1.4084</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.4971</v>
+        <v>-1.4084</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.4971</v>
+        <v>-1.4084</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.4971</v>
+        <v>-1.4084</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.4971</v>
+        <v>-1.4084</v>
       </c>
       <c r="N74" t="n">
-        <v>95</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NickelBack</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.704</v>
+        <v>-1.4971</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8986</v>
+        <v>-0.7895</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1097</v>
+        <v>-1.0404</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.704</v>
+        <v>-1.4971</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.704</v>
+        <v>-1.4971</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.704</v>
+        <v>-1.4971</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.704</v>
+        <v>-1.4971</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>258</v>
+        <v>95</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.704</v>
+        <v>-1.4971</v>
       </c>
       <c r="N75" t="n">
-        <v>258</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NickelBack</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7088</v>
+        <v>-1.704</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9011</v>
+        <v>-0.8986</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1117</v>
+        <v>-1.1228</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7088</v>
+        <v>-1.704</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.7088</v>
+        <v>-1.704</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.7088</v>
+        <v>-1.704</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.7088</v>
+        <v>-1.704</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.7088</v>
+        <v>-1.704</v>
       </c>
       <c r="N76" t="n">
-        <v>151</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77">
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.8254</v>
+        <v>-1.7502</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9626</v>
+        <v>-0.923</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1588</v>
+        <v>-1.1412</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.8254</v>
+        <v>-1.7502</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.688</v>
+        <v>-1.6128</v>
       </c>
       <c r="G77" t="n">
         <v>-0.1374</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.688</v>
+        <v>-1.6128</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.688</v>
+        <v>-1.6128</v>
       </c>
       <c r="J77" t="n">
         <v>-0.1374</v>
@@ -3979,7 +3979,7 @@
         <v>54</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.8254</v>
+        <v>-1.7502</v>
       </c>
       <c r="N77" t="n">
         <v>291</v>
@@ -3988,139 +3988,139 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.3381</v>
+        <v>-2.2903</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.233</v>
+        <v>-1.2078</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3659</v>
+        <v>-1.3564</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.3381</v>
+        <v>-2.2903</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.3381</v>
+        <v>-1.2903</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.3381</v>
+        <v>-1.2903</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.3381</v>
+        <v>-1.2903</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K78" t="n">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.3381</v>
+        <v>-2.2903</v>
       </c>
       <c r="N78" t="n">
-        <v>118</v>
+        <v>291</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.6858</v>
+        <v>-2.3381</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.4164</v>
+        <v>-1.233</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5064</v>
+        <v>-1.3754</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.6858</v>
+        <v>-2.3381</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.139</v>
+        <v>-2.3381</v>
       </c>
       <c r="G79" t="n">
-        <v>-1.5468</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.139</v>
+        <v>-2.3381</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.139</v>
+        <v>-2.3381</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.5468</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="L79" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.6858</v>
+        <v>-2.3381</v>
       </c>
       <c r="N79" t="n">
-        <v>314</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3</v>
+        <v>-2.6287</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.5821</v>
+        <v>-1.3863</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6333</v>
+        <v>-1.4912</v>
       </c>
       <c r="E80" t="n">
-        <v>-3</v>
+        <v>-2.6287</v>
       </c>
       <c r="F80" t="n">
-        <v>-2</v>
+        <v>-1.0819</v>
       </c>
       <c r="G80" t="n">
-        <v>-1</v>
+        <v>-1.5468</v>
       </c>
       <c r="H80" t="n">
-        <v>-2</v>
+        <v>-1.0819</v>
       </c>
       <c r="I80" t="n">
-        <v>-2</v>
+        <v>-1.0819</v>
       </c>
       <c r="J80" t="n">
-        <v>-1</v>
+        <v>-1.5468</v>
       </c>
       <c r="K80" t="n">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="L80" t="n">
-        <v>54</v>
+        <v>210</v>
       </c>
       <c r="M80" t="n">
-        <v>-3</v>
+        <v>-2.6287</v>
       </c>
       <c r="N80" t="n">
-        <v>291</v>
+        <v>314</v>
       </c>
     </row>
     <row r="81">
@@ -4136,7 +4136,7 @@
         <v>-1.75</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.762</v>
+        <v>-1.766</v>
       </c>
       <c r="E81" t="n">
         <v>-3.3185</v>
